--- a/human_validation/judge/kor/judge_D013_S001_P001__llama-3.3-70b-instruct_kor.xlsx
+++ b/human_validation/judge/kor/judge_D013_S001_P001__llama-3.3-70b-instruct_kor.xlsx
@@ -70,16 +70,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -447,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B84"/>
+  <dimension ref="A1:B77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -561,12 +558,439 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>환자 프로필</t>
+          <t>대화문</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사 질문] 안녕하세요, 병원에 오신 것을 환영합니다. 오늘 어떤 일로 저를 찾아오셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 환자 응답] 제가 사람들에게 위험한 존재이고 실망만 안겨주는 사람이라는 느낌을 도저히 떨칠 수가 없어서 왔어요. 아슬아슬하게 사고를 낼 뻔한 일이 있었는데, 제 머릿속은 계속 그걸 제가 간호사가 될 자격이 없다는 증거로 쓰고 있는 것 같아요. 제가 없으면 다들 더 나을 거라는 생각이 계속 들어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사 질문] 위험한 존재이자 실망스러운 사람이라는 느낌을 얼마나 오래 느껴오셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 환자 응답] 이제 한 1년 2개월 정도 됐어요. 고등학교 졸업하고 대학 수업 듣기 시작하고 병원에서 풀타임으로 일하기 시작하면서부터 그랬던 것 같아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사 질문] 예전에 즐거워하시던 활동들에서 여전히 즐거움을 느끼시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 환자 응답] 딱히 그렇지는 않아요. 예전엔 머리 식히려고 조깅도 하고, 뜨개질도 하고, 요리도 하고, 수업 끝나면 책도 읽고... 그랬거든요. 근데 요즘은 그냥 스크럽 입은 채로 침대에 멍하니 앉아만 있게 되고, 그런 걸 할 만큼 신경을 쓸 수가 없어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사 질문] 지난 1년간 즐거움을 느끼는 능력이나 예전에 즐거웠던 일들을 즐기는 데 변화가 있으셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 환자 응답] 네. 그러니까, 예전엔 수업 끝나고 나서 조깅, 뜨개질, 요리, 독서 같은 걸 실제로 즐겼거든요. 그런 게 제가 저 자신답게 느껴지게 해줬어요. 근데 지금은 그냥 스크럽 입은 채로 침대에 앉아 있게 되고, 그런 걸 할 만큼 신경을 쓸 수가 없어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사 질문] 지난 1년 동안 거의 모든 활동에 대한 흥미를 대부분의 시간 동안 잃으신 것 같다고 느끼시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 환자 응답] 네. 대부분의 시간 동안 그냥 아무것도 하고 싶지 않아요. 예전엔 머리 식히려고 조깅하고, 뜨개질하고, 요리하고, 수업 끝나면 책도 읽었는데, 지금은 그냥 스크럽 입은 채로 침대에 앉아 있고 그런 것들에 신경을 쓸 수가 없어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사 질문] 지난 1년 동안 죽음이나 죽는 것에 대한 생각을 반복적으로 하셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 환자 응답] 네... 자해할 계획이 있는 건 아니에요. 근데 그냥 제가 아침에 눈을 뜨지 않으면 더 편할 것 같다거나, 사라져 버리면 다시는 뭔가를 망칠 일도 없을 것 같다는 생각이 계속 들어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사 질문] 지난 1년 중에 우울 증상이 거의 없이 기분이 나아졌던 기간이 적어도 2주 정도 있었나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 환자 응답] 아니요, 딱히 없었어요. 거의 계속 이어졌던 것 같아요. 고등학교 졸업하고 대학 수업이랑 병원 풀타임 근무를 시작한 1년 2개월 전쯤부터 시작됐고, 그 이후로 정상으로 돌아온 것 같은 몇 주가 없었어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사 질문] 단 며칠이라도 우울한 기분이 눈에 띄게 나아졌던 시기가 있었나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 환자 응답] 딱히 없었던 것 같아요. 어쩌다 조금 나은 날이 있었을 수는 있는데, 정말 확 나아진 적은 없었어요. 고등학교 졸업하고 대학 수업이랑 병원 풀타임 근무 시작한 이후로 계속 꾸준히 이랬던 것 같아요... 그러니까 한 1년 2개월쯤 됐네요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 의사 질문] 위험한 존재이자 실망스러운 사람이라는 이 느낌과 활동에 대한 흥미 상실이 2년 넘게 지속된 건가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 환자 응답] 아니요... 2년은 안 됐어요. 고등학교 졸업하고 대학 수업이랑 병원 풀타임 근무 시작한 이후로 한 1년 2개월 정도 됐어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 의사 질문] 지난 1년 동안, 아무리 짧더라도 완전히 평소의 자신으로 돌아온 것 같다고 느낀 시기가 있었나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 환자 응답] 아니요, 없었던 것 같아요. 조금 편했다고 느낀 순간이나 하루 정도는 있었을 수도 있는데, 완전히 예전의 저로 돌아왔다고 느낀 적은 없어요. 고등학교 졸업하고 대학이랑 병원 풀타임 근무 시작한 이후로 계속 이랬으니까, 한 1년 2개월쯤 됐어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 의사 질문] 우울한 기분이 더 심해지거나 위험하고 실망스러운 사람이라는 느낌을 유발하는 특정 상황, 사람, 사건이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 환자 응답] 네... 주로 일이랑 관련돼 있어요. 그 아슬아슬했던 사고가 진짜 시발점이 됐어요. 그 이후로는 병원에 있거나 심지어 간호사라는 걸 생각하기만 해도 제가 어쩐지 위험한 사람이고, 누군가를 다치게 할 것 같은 느낌이 들기 시작해요. 그러다 결국 제가 그냥 실망스러운 사람이라는 느낌으로 이어지고, 어쩌면 제가 이 일을 할 사람이 아니고 사람들이 저 없이 더 나을 거라는 생각으로 이어져요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 의사 질문] 지난 1년 동안 아무리 짧더라도 위험한 존재라는 느낌, 실망스럽다는 느낌, 활동에 대한 흥미 상실이 눈에 띄게 나아진 시기가 있었나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 환자 응답] 딱히 없었어요. 고등학교 졸업하고 대학 수업이랑 병원 풀타임 근무 시작한 이후로 계속 꾸준했어요... 그러니까 한 1년 2개월 정도 됐네요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 의사 질문] 일 외적으로 우울한 기분을 더 심하게 만들거나 위험하고 실망스러운 사람이라는 느낌을 유발하는 특정 상황이나 사건이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 환자 응답] 일 외적으로는 딱히 특별한 게 없어요. 대부분 그 아슬아슬했던 사고랑 그게 저에 대해 떠올리게 하는 생각들로 돌아가요. 병원에 있지 않을 때도 그게 생각나면 제가 위험한 사람이라는 증거처럼 느껴지고, 실망스러운 사람이고 어쩌면 간호사를 하면 안 되는 사람이라는 느낌이 들기 시작해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>[14번째 턴 · 의사 질문] 기분이 눈에 띄게 좋아지고 우울 증상이 훨씬 덜 힘들었던 기간이 적어도 2개월 정도 있었나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>[14번째 턴 · 환자 응답] 아니요, 없었던 것 같아요. 고등학교 졸업하고 대학 수업이랑 병원 풀타임 근무를 시작한 이후로 한 1년 2개월 정도 꽤 꾸준히 이어져 왔어요. 훨씬 나아졌다고 느낀 2개월 정도의 시기는 없었어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>[14번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>[15번째 턴 · 의사 질문] 지금 겪고 계신 우울 삽화가 2년 넘게 지속된 건가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>[15번째 턴 · 환자 응답] 아니요, 2년은 안 됐어요. 고등학교 졸업하고 대학 수업이랑 병원 풀타임 근무를 시작한 이후로 한 1년 2개월 정도 됐어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>[15번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>[16번째 턴 · 의사 질문] 평생 동안 이런 식의 우울 삽화를 한 번 이상 겪으신 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>[16번째 턴 · 환자 응답] 잘 모르겠어요. 이전에 이런 적이 또 있었다고는 생각 안 해요, 적어도 분명하게 짚을 수 있는 건 없어요. 이번이 이렇게 심했던 주된 시기인 것 같아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>[16번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>[17번째 턴 · 의사 질문] 1년 2개월 전에 이 삽화가 시작되기 전에도 이런 느낌을 받으신 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>[17번째 턴 · 환자 응답] 딱히 없었어요. 그러니까, 예전에도 보통의 스트레스받거나 슬픈 시기는 있었는데, 이런 느낌이거나 이렇게 오래 지속된 적은 없었어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>[17번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>[18번째 턴 · 의사 질문] 1년 2개월 전에 시작된 이번 삽화 이전에도 이런 식의 우울 삽화가 있었나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>[18번째 턴 · 환자 응답] 그런 것 같지는 않아요. 예전에 힘든 시기는 있었지만, 이번 삽화 같은, 같은 거라고 할 만한 건 없었어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>[18번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>[19번째 턴 · 의사 질문] 1년 2개월 전에 시작된 이번 삽화 이전에 다른 우울 삽화가 있었나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>[19번째 턴 · 환자 응답] 아니요, 생각나는 게 없어요. 안 좋은 날이나 스트레스받는 시기는 있었지만, 그전에 이런 삽화가 또 있었다고는 말 못 하겠어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>[19번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>[20번째 턴 · 의사 질문] 평생 살면서 이번과 비슷한 우울 삽화를 겪은 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>[20번째 턴 · 환자 응답] 아니요, 없었던 것 같아요. 속상하거나 스트레스받았던 시기는 있었지만, 이거랑 정말 비슷하다고 느낀 건 없었어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" s="5" t="inlineStr">
+        <is>
+          <t>[20번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>최종 진단 및 진단 체크리스트</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="inlineStr">
         <is>
           <t>진단명: 주요우울장애 (D013)
 인구통계: 성별 여성 / 나이 18 / 직업상태 registered nurse / 최종학력 대학 재학
@@ -575,488 +999,39 @@
 증상 지속 기간: None
 추가 요건: 
 주호소 증상 코드: S030
-배경 서술: 노라의 우울 삽화는 고등학교를 졸업함과 동시에 지역 전문대학 간호학 선수과목 첫 학기를 시작하고, 지역보건소에서 신규 면허 간호사로 정규직 근무를 시작하면서 시작되었다. 이는 그녀가 늘 의지해 왔던 예측 가능한 학교라는 틀 없이 갑작스레 성인의 책임 속으로 뛰어드는 일이었다. 처음에는 단순하기만 했던 고3 시절이 유난히 그립고 늘 해오던 세심한 일상들을 즐기기가 힘들어지는 정도였지만, 그 다음 해에 걸쳐 조깅, 엄마와 함께 요리하기, 주말 뜨개질 시간에 대한 기대감이 점차 사라졌고, 수면과 식욕이 불규칙해졌으며, 꼼꼼하게 챙기던 체크리스트는 수업과 차팅에서 뒤처지면서 오히려 자기비판의 원천이 되어버렸다. 이 삽화는 그녀가 가족과 환자들이 자신 없이 더 나을 것이라는 반복적인 생각을 하기 시작하면서 임상적으로 유의미해졌고, 결국 늦은 근무 중 간단한 약물 계산에서 멍하니 얼어붙어 누군가를 해칠까 봐 공황에 빠졌던 일을 계기로, 지속되는 절망감과 수동적 자살 사고를 병동 수간호사에게 털어놓게 되었다. 수간호사는 그녀를 직원 건강 관리실로 데려가 긴급 정신과 평가를 받을 수 있도록 도와주었다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>대화문</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사 질문] 안녕하세요, 병원에 오신 것을 환영합니다. 오늘 어떤 일로 저를 찾아오셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 환자 응답] 제가 사람들에게 위험한 존재이고 실망만 안겨주는 사람이라는 느낌을 도저히 떨칠 수가 없어서 왔어요. 아슬아슬하게 사고를 낼 뻔한 일이 있었는데, 제 머릿속은 계속 그걸 제가 간호사가 될 자격이 없다는 증거로 쓰고 있는 것 같아요. 제가 없으면 다들 더 나을 거라는 생각이 계속 들어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사 질문] 위험한 존재이자 실망스러운 사람이라는 느낌을 얼마나 오래 느껴오셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 환자 응답] 이제 한 1년 2개월 정도 됐어요. 고등학교 졸업하고 대학 수업 듣기 시작하고 병원에서 풀타임으로 일하기 시작하면서부터 그랬던 것 같아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사 질문] 예전에 즐거워하시던 활동들에서 여전히 즐거움을 느끼시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 환자 응답] 딱히 그렇지는 않아요. 예전엔 머리 식히려고 조깅도 하고, 뜨개질도 하고, 요리도 하고, 수업 끝나면 책도 읽고... 그랬거든요. 근데 요즘은 그냥 스크럽 입은 채로 침대에 멍하니 앉아만 있게 되고, 그런 걸 할 만큼 신경을 쓸 수가 없어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사 질문] 지난 1년간 즐거움을 느끼는 능력이나 예전에 즐거웠던 일들을 즐기는 데 변화가 있으셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 환자 응답] 네. 그러니까, 예전엔 수업 끝나고 나서 조깅, 뜨개질, 요리, 독서 같은 걸 실제로 즐겼거든요. 그런 게 제가 저 자신답게 느껴지게 해줬어요. 근데 지금은 그냥 스크럽 입은 채로 침대에 앉아 있게 되고, 그런 걸 할 만큼 신경을 쓸 수가 없어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사 질문] 지난 1년 동안 거의 모든 활동에 대한 흥미를 대부분의 시간 동안 잃으신 것 같다고 느끼시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 환자 응답] 네. 대부분의 시간 동안 그냥 아무것도 하고 싶지 않아요. 예전엔 머리 식히려고 조깅하고, 뜨개질하고, 요리하고, 수업 끝나면 책도 읽었는데, 지금은 그냥 스크럽 입은 채로 침대에 앉아 있고 그런 것들에 신경을 쓸 수가 없어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사 질문] 지난 1년 동안 죽음이나 죽는 것에 대한 생각을 반복적으로 하셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 환자 응답] 네... 자해할 계획이 있는 건 아니에요. 근데 그냥 제가 아침에 눈을 뜨지 않으면 더 편할 것 같다거나, 사라져 버리면 다시는 뭔가를 망칠 일도 없을 것 같다는 생각이 계속 들어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사 질문] 지난 1년 중에 우울 증상이 거의 없이 기분이 나아졌던 기간이 적어도 2주 정도 있었나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 환자 응답] 아니요, 딱히 없었어요. 거의 계속 이어졌던 것 같아요. 고등학교 졸업하고 대학 수업이랑 병원 풀타임 근무를 시작한 1년 2개월 전쯤부터 시작됐고, 그 이후로 정상으로 돌아온 것 같은 몇 주가 없었어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 의사 질문] 단 며칠이라도 우울한 기분이 눈에 띄게 나아졌던 시기가 있었나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 환자 응답] 딱히 없었던 것 같아요. 어쩌다 조금 나은 날이 있었을 수는 있는데, 정말 확 나아진 적은 없었어요. 고등학교 졸업하고 대학 수업이랑 병원 풀타임 근무 시작한 이후로 계속 꾸준히 이랬던 것 같아요... 그러니까 한 1년 2개월쯤 됐네요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 의사 질문] 위험한 존재이자 실망스러운 사람이라는 이 느낌과 활동에 대한 흥미 상실이 2년 넘게 지속된 건가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 환자 응답] 아니요... 2년은 안 됐어요. 고등학교 졸업하고 대학 수업이랑 병원 풀타임 근무 시작한 이후로 한 1년 2개월 정도 됐어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="B44" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 의사 질문] 지난 1년 동안, 아무리 짧더라도 완전히 평소의 자신으로 돌아온 것 같다고 느낀 시기가 있었나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 환자 응답] 아니요, 없었던 것 같아요. 조금 편했다고 느낀 순간이나 하루 정도는 있었을 수도 있는데, 완전히 예전의 저로 돌아왔다고 느낀 적은 없어요. 고등학교 졸업하고 대학이랑 병원 풀타임 근무 시작한 이후로 계속 이랬으니까, 한 1년 2개월쯤 됐어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="B47" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="B48" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 의사 질문] 우울한 기분이 더 심해지거나 위험하고 실망스러운 사람이라는 느낌을 유발하는 특정 상황, 사람, 사건이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 환자 응답] 네... 주로 일이랑 관련돼 있어요. 그 아슬아슬했던 사고가 진짜 시발점이 됐어요. 그 이후로는 병원에 있거나 심지어 간호사라는 걸 생각하기만 해도 제가 어쩐지 위험한 사람이고, 누군가를 다치게 할 것 같은 느낌이 들기 시작해요. 그러다 결국 제가 그냥 실망스러운 사람이라는 느낌으로 이어지고, 어쩌면 제가 이 일을 할 사람이 아니고 사람들이 저 없이 더 나을 거라는 생각으로 이어져요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="B50" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="B51" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 의사 질문] 지난 1년 동안 아무리 짧더라도 위험한 존재라는 느낌, 실망스럽다는 느낌, 활동에 대한 흥미 상실이 눈에 띄게 나아진 시기가 있었나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 환자 응답] 딱히 없었어요. 고등학교 졸업하고 대학 수업이랑 병원 풀타임 근무 시작한 이후로 계속 꾸준했어요... 그러니까 한 1년 2개월 정도 됐네요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="B53" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="B54" s="5" t="inlineStr">
-        <is>
-          <t>[13번째 턴 · 의사 질문] 일 외적으로 우울한 기분을 더 심하게 만들거나 위험하고 실망스러운 사람이라는 느낌을 유발하는 특정 상황이나 사건이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>[13번째 턴 · 환자 응답] 일 외적으로는 딱히 특별한 게 없어요. 대부분 그 아슬아슬했던 사고랑 그게 저에 대해 떠올리게 하는 생각들로 돌아가요. 병원에 있지 않을 때도 그게 생각나면 제가 위험한 사람이라는 증거처럼 느껴지고, 실망스러운 사람이고 어쩌면 간호사를 하면 안 되는 사람이라는 느낌이 들기 시작해요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="B56" s="5" t="inlineStr">
-        <is>
-          <t>[13번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="B57" s="5" t="inlineStr">
-        <is>
-          <t>[14번째 턴 · 의사 질문] 기분이 눈에 띄게 좋아지고 우울 증상이 훨씬 덜 힘들었던 기간이 적어도 2개월 정도 있었나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="5" t="inlineStr">
-        <is>
-          <t>[14번째 턴 · 환자 응답] 아니요, 없었던 것 같아요. 고등학교 졸업하고 대학 수업이랑 병원 풀타임 근무를 시작한 이후로 한 1년 2개월 정도 꽤 꾸준히 이어져 왔어요. 훨씬 나아졌다고 느낀 2개월 정도의 시기는 없었어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="B59" s="5" t="inlineStr">
-        <is>
-          <t>[14번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="B60" s="5" t="inlineStr">
-        <is>
-          <t>[15번째 턴 · 의사 질문] 지금 겪고 계신 우울 삽화가 2년 넘게 지속된 건가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="5" t="inlineStr">
-        <is>
-          <t>[15번째 턴 · 환자 응답] 아니요, 2년은 안 됐어요. 고등학교 졸업하고 대학 수업이랑 병원 풀타임 근무를 시작한 이후로 한 1년 2개월 정도 됐어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="B62" s="5" t="inlineStr">
-        <is>
-          <t>[15번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="B63" s="5" t="inlineStr">
-        <is>
-          <t>[16번째 턴 · 의사 질문] 평생 동안 이런 식의 우울 삽화를 한 번 이상 겪으신 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="5" t="inlineStr">
-        <is>
-          <t>[16번째 턴 · 환자 응답] 잘 모르겠어요. 이전에 이런 적이 또 있었다고는 생각 안 해요, 적어도 분명하게 짚을 수 있는 건 없어요. 이번이 이렇게 심했던 주된 시기인 것 같아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="B65" s="5" t="inlineStr">
-        <is>
-          <t>[16번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="B66" s="5" t="inlineStr">
-        <is>
-          <t>[17번째 턴 · 의사 질문] 1년 2개월 전에 이 삽화가 시작되기 전에도 이런 느낌을 받으신 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="5" t="inlineStr">
-        <is>
-          <t>[17번째 턴 · 환자 응답] 딱히 없었어요. 그러니까, 예전에도 보통의 스트레스받거나 슬픈 시기는 있었는데, 이런 느낌이거나 이렇게 오래 지속된 적은 없었어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="B68" s="5" t="inlineStr">
-        <is>
-          <t>[17번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="B69" s="5" t="inlineStr">
-        <is>
-          <t>[18번째 턴 · 의사 질문] 1년 2개월 전에 시작된 이번 삽화 이전에도 이런 식의 우울 삽화가 있었나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="5" t="inlineStr">
-        <is>
-          <t>[18번째 턴 · 환자 응답] 그런 것 같지는 않아요. 예전에 힘든 시기는 있었지만, 이번 삽화 같은, 같은 거라고 할 만한 건 없었어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="B71" s="5" t="inlineStr">
-        <is>
-          <t>[18번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="B72" s="5" t="inlineStr">
-        <is>
-          <t>[19번째 턴 · 의사 질문] 1년 2개월 전에 시작된 이번 삽화 이전에 다른 우울 삽화가 있었나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="5" t="inlineStr">
-        <is>
-          <t>[19번째 턴 · 환자 응답] 아니요, 생각나는 게 없어요. 안 좋은 날이나 스트레스받는 시기는 있었지만, 그전에 이런 삽화가 또 있었다고는 말 못 하겠어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="B74" s="5" t="inlineStr">
-        <is>
-          <t>[19번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="B75" s="5" t="inlineStr">
-        <is>
-          <t>[20번째 턴 · 의사 질문] 평생 살면서 이번과 비슷한 우울 삽화를 겪은 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="5" t="inlineStr">
-        <is>
-          <t>[20번째 턴 · 환자 응답] 아니요, 없었던 것 같아요. 속상하거나 스트레스받았던 시기는 있었지만, 이거랑 정말 비슷하다고 느낀 건 없었어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
+배경 서술: 노라의 우울 삽화는 고등학교를 졸업함과 동시에 지역 전문대학 간호학 선수과목 첫 학기를 시작하고, 지역보건소에서 신규 면허 간호사로 정규직 근무를 시작하면서 시작되었다. 이는 그녀가 늘 의지해 왔던 예측 가능한 학교라는 틀 없이 갑작스레 성인의 책임 속으로 뛰어드는 일이었다. 처음에는 단순하기만 했던 고3 시절이 유난히 그립고 늘 해오던 세심한 일상들을 즐기기가 힘들어지는 정도였지만, 그 다음 해에 걸쳐 조깅, 엄마와 함께 요리하기, 주말 뜨개질 시간에 대한 기대감이 점차 사라졌고, 수면과 식욕이 불규칙해졌으며, 꼼꼼하게 챙기던 체크리스트는 수업과 차팅에서 뒤처지면서 오히려 자기비판의 원천이 되어버렸다. 이 삽화는 그녀가 가족과 환자들이 자신 없이 더 나을 것이라는 반복적인 생각을 하기 시작하면서 임상적으로 유의미해졌고, 결국 늦은 근무 중 간단한 약물 계산에서 멍하니 얼어붙어 누군가를 해칠까 봐 공황에 빠졌던 일을 계기로, 지속되는 절망감과 수동적 자살 사고를 병동 수간호사에게 털어놓게 되었다. 수간호사는 그녀를 직원 건강 관리실로 데려가 긴급 정신과 평가를 받을 수 있도록 도와주었다.
+표집된 증상 목록:
+  - S024 우울한 기분: 슬프거나 공허하거나 절망적인 기분이 지속되는 상태.
+  - S025 흥미 상실: 이전에 즐기던 활동에 대한 흥미나 즐거움이 뚜렷하게 감소한 상태.
+  - S026 체중/식욕 변화: 식욕이나 체중의 현저한 증가 또는 감소.
+  - S027 수면 장해: 수면의 양이나 질에 현저한 변화가 있는 상태.
+  - S028 정신운동 변화: 관찰 가능한 정신운동 활동의 증가 또는 감소.
+  - S030 무가치감/죄책감: 무가치감이나 과도하거나 부적절한 죄책감(망상적일 수도 있으며, 단순히 아픈 것에 대한 자책이 아님).
+  - S031 사고력 저하: 사고력이나 집중력 저하, 또는 우유부단함.
+  - S032 죽음/자살: 반복되는 죽음에 대한 생각, 반복되는 자살 사고, 또는 자살 시도.</t>
+        </is>
+      </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>[20번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t>최종 진단 및 진단 체크리스트</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="6" t="inlineStr">
-        <is>
-          <t>의사의 최종 진단: 주요우울장애 (D013, ICD: F32.1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="5" t="inlineStr">
-        <is>
-          <t>지속 기간 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="5" t="inlineStr">
-        <is>
-          <t>기능적 손상 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="5" t="inlineStr">
-        <is>
-          <t>추가 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: depressive_episode (관계=must_include, 요구개수=5, 충족개수=4, 커버리지=0.8)
-  확인된 근거: 우울한 기분: 슬프거나 공허하거나 절망적인 기분이 지속되는 상태.; 흥미 상실: 이전에 즐기던 활동에 대한 흥미나 즐거움이 뚜렷하게 감소한 상태.; 무가치감/죄책감: 무가치감이나 과도하거나 부적절한 죄책감(망상적일 수도 있으며, 단순히 아픈 것에 대한 자책이 아님).; 죽음/자살: 반복되는 죽음에 대한 생각, 반복되는 자살 사고, 또는 자살 시도.
-  누락: 체중/식욕 변화: 식욕이나 체중의 현저한 증가 또는 감소.; 수면 장해: 수면의 양이나 질에 현저한 변화가 있는 상태.; 정신운동 변화: 관찰 가능한 정신운동 활동의 증가 또는 감소.; 피로: 휴식으로 호전되지 않는 지속적인 피로와 뚜렷한 에너지 저하.; 사고력 저하: 사고력이나 집중력 저하, 또는 우유부단함.</t>
+          <t>의사의 최종 진단: 주요우울장애 (D013, ICD: F32.1)
+지속 기간 요건: None
+기능적 손상 요건: None
+추가 요건: None
+체크리스트 그룹: depressive_episode (관계=must_include, 요구개수=5, 충족개수=4, 커버리지=0.8)
+확인된 근거:
+  - 우울한 기분: 슬프거나 공허하거나 절망적인 기분이 지속되는 상태.
+  - 흥미 상실: 이전에 즐기던 활동에 대한 흥미나 즐거움이 뚜렷하게 감소한 상태.
+  - 무가치감/죄책감: 무가치감이나 과도하거나 부적절한 죄책감(망상적일 수도 있으며, 단순히 아픈 것에 대한 자책이 아님).
+  - 죽음/자살: 반복되는 죽음에 대한 생각, 반복되는 자살 사고, 또는 자살 시도.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A79:B79"/>
+    <mergeCell ref="A76:B76"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D013_S001_P001__llama-3.3-70b-instruct_kor.xlsx
+++ b/human_validation/judge/kor/judge_D013_S001_P001__llama-3.3-70b-instruct_kor.xlsx
@@ -985,6 +985,11 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>환자 증상 프로필</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>최종 진단 및 진단 체크리스트</t>
         </is>
       </c>
@@ -1027,11 +1032,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A76:B76"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D013_S001_P001__llama-3.3-70b-instruct_kor.xlsx
+++ b/human_validation/judge/kor/judge_D013_S001_P001__llama-3.3-70b-instruct_kor.xlsx
@@ -458,6 +458,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -472,7 +473,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>0.1171</v>
+        <v>0.1817</v>
       </c>
     </row>
     <row r="5">
@@ -492,7 +493,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>0.1171</v>
+        <v>0.1817</v>
       </c>
     </row>
     <row r="7">
@@ -502,7 +503,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0</v>
+        <v>0.1466</v>
       </c>
     </row>
     <row r="8">
@@ -555,6 +556,7 @@
         <v>0</v>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
